--- a/teacher_forms/006_international_school_application_form--teacher_forms.xlsx
+++ b/teacher_forms/006_international_school_application_form--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>armenia</t>
+          <t>aruba</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Aruba</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>aruba</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>australia</t>
+          <t>austria</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Austria</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>austria</t>
+          <t>azerbaijan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>student_country_choices</t>
+          <t>guardian_country_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>azerbaijan</t>
+          <t>afghanistan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Afghanistan</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>afghanistan</t>
+          <t>albania</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Albania</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>albania</t>
+          <t>algeria</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Algeria</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>algeria</t>
+          <t>andorra</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Andorra</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>andorra</t>
+          <t>angola</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Angola</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>angola</t>
+          <t>antigua_and_barbuda</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Antigua and Barbuda</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>antigua_and_barbuda</t>
+          <t>argentina</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Antigua and Barbuda</t>
+          <t>Argentina</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>argentina</t>
+          <t>armenia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Armenia</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>armenia</t>
+          <t>aruba</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Aruba</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>armenia</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>aruba</t>
+          <t>austria</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Austria</t>
         </is>
       </c>
     </row>
@@ -1522,46 +1522,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>australia</t>
+          <t>azerbaijan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>guardian_country_choices</t>
+          <t>preferred_language_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>austria</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>guardian_country_choices</t>
+          <t>preferred_language_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>azerbaijan</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>japanese</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>german</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>japanese</t>
+          <t>russian</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Russian</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>mandarin</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>russian</t>
+          <t>swedish</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russian</t>
+          <t>Swedish</t>
         </is>
       </c>
     </row>
@@ -1675,46 +1675,46 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>vietnamese</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Vietnamese</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>preferred_language_choices</t>
+          <t>teacher_country_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>swedish</t>
+          <t>afghanistan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Swedish</t>
+          <t>Afghanistan</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>preferred_language_choices</t>
+          <t>teacher_country_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>vietnamese</t>
+          <t>albania</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vietnamese</t>
+          <t>Albania</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>afghanistan</t>
+          <t>algeria</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Algeria</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>albania</t>
+          <t>andorra</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Andorra</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>algeria</t>
+          <t>angola</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Angola</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>andorra</t>
+          <t>antigua_and_barbuda</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Antigua and Barbuda</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>angola</t>
+          <t>argentina</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Argentina</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>antigua_and_barbuda</t>
+          <t>armenia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Antigua and Barbuda</t>
+          <t>Armenia</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>argentina</t>
+          <t>aruba</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Aruba</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>armenia</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>armenia</t>
+          <t>austria</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Austria</t>
         </is>
       </c>
     </row>
@@ -1879,63 +1879,63 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>aruba</t>
+          <t>azerbaijan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>teacher_country_choices</t>
+          <t>student_language_proficiency_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>australia</t>
+          <t>afghan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Afghan</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>teacher_country_choices</t>
+          <t>student_language_proficiency_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>austria</t>
+          <t>albanian</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Albanian</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>teacher_country_choices</t>
+          <t>student_language_proficiency_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>azerbaijan</t>
+          <t>algerian</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Algerian</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>afghan</t>
+          <t>arabic</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Afghan</t>
+          <t>Arabic</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>albanian</t>
+          <t>armenian</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Albanian</t>
+          <t>Armenian</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>algerian</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algerian</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>arabic</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>armenian</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Armenian</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>japanese</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>german</t>
+          <t>russian</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>Russian</t>
         </is>
       </c>
     </row>
@@ -2100,61 +2100,10 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>japanese</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
-        <is>
-          <t>Japanese</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>student_language_proficiency_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>mandarin</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Mandarin</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>student_language_proficiency_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>russian</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Russian</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>student_language_proficiency_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>spanish</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
         <is>
           <t>Spanish</t>
         </is>
